--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AB6FCC9-6172-4C5A-970A-5D81EF502C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA857865-E8FB-4063-9B4E-3C453DBCF897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Instructions" sheetId="1" r:id="rId1"/>
+    <sheet name="cv_entries" sheetId="3" r:id="rId1"/>
     <sheet name="Column guide" sheetId="2" r:id="rId2"/>
-    <sheet name="cv_entries" sheetId="3" r:id="rId3"/>
+    <sheet name="Instructions" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
   <extLst>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="168">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="200">
   <si>
     <t>cv_data.xlsx - how this works</t>
   </si>
@@ -314,48 +314,27 @@
     <t>Ecological Careers Workshop</t>
   </si>
   <si>
-    <t>Physiological tools for monitoring urban impacts at the roost level in insectivorous bats</t>
-  </si>
-  <si>
     <t>Joint Conference of the Australian Mammal Society and Australasian Bat Society, Australia</t>
   </si>
   <si>
     <t>Talk</t>
   </si>
   <si>
-    <t>Bats Are In The Building: Understanding Anthropogenic Roost Selection Through Habitat Models</t>
-  </si>
-  <si>
     <t>Ecological Society of Australia Conference, Australia</t>
   </si>
   <si>
-    <t>Stressed out bats: developing tools to monitor physiological stress in three insectivorous species</t>
-  </si>
-  <si>
     <t>Australian and New Zealand Society for Comparative Physiology and Biochemistry Meeting, Australia</t>
   </si>
   <si>
     <t>20th International Bat Research Conference, Australia</t>
   </si>
   <si>
-    <t>The system works: post-release survival of rehabilitated insectivorous bats in Australia</t>
-  </si>
-  <si>
-    <t>Home is where the bats are: Bats in man-made structures in South East Queensland</t>
-  </si>
-  <si>
     <t>Animal Ecology Seminar Series, The University of the Sunshine Coast, Australia</t>
   </si>
   <si>
-    <t>From rugs to rocky overhangs: diverse microclimates of natural and anthropogenic bat roosts in South East Queensland</t>
-  </si>
-  <si>
     <t>21st Australasian Bat Society Conference, Australia</t>
   </si>
   <si>
-    <t>Roosting Ecology of Australian Insectivorous Bats, a Public Dataset</t>
-  </si>
-  <si>
     <t>Australasian Bat Society Conference, Australia</t>
   </si>
   <si>
@@ -531,17 +510,133 @@
   </si>
   <si>
     <t>No One Size Fits All: Exploring Anthropogenic Roost Selection Across an Urban Gradient in South East Queensland</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2020</t>
+  </si>
+  <si>
+    <t>Apr-2024</t>
+  </si>
+  <si>
+    <t>Apr-2026</t>
+  </si>
+  <si>
+    <t>Oct-2025</t>
+  </si>
+  <si>
+    <t>Jul-2025</t>
+  </si>
+  <si>
+    <t>Sep-2024</t>
+  </si>
+  <si>
+    <t>Aug-2026</t>
+  </si>
+  <si>
+    <t>Nov-2025</t>
+  </si>
+  <si>
+    <t>Dec-2025</t>
+  </si>
+  <si>
+    <t>Aug-2025</t>
+  </si>
+  <si>
+    <t>Oct-2024</t>
+  </si>
+  <si>
+    <t>Nov-2023</t>
+  </si>
+  <si>
+    <t>Feb-2020</t>
+  </si>
+  <si>
+    <t>Dec-2019</t>
+  </si>
+  <si>
+    <t>Oct-2018</t>
+  </si>
+  <si>
+    <t>Apr-2015</t>
+  </si>
+  <si>
+    <t>Apr-2016</t>
+  </si>
+  <si>
+    <t>28-Jan-2026</t>
+  </si>
+  <si>
+    <t>25-Jan-2026</t>
+  </si>
+  <si>
+    <t>28-Aug-2024</t>
+  </si>
+  <si>
+    <t>25-Jul-2024</t>
+  </si>
+  <si>
+    <t>23-Feb-2024</t>
+  </si>
+  <si>
+    <t>09-Feb-2024</t>
+  </si>
+  <si>
+    <t>25-Jul-2023</t>
+  </si>
+  <si>
+    <t>Mar-2026</t>
+  </si>
+  <si>
+    <t>Nov-2024</t>
+  </si>
+  <si>
+    <t>May-2024</t>
+  </si>
+  <si>
+    <t>Oct-2023</t>
+  </si>
+  <si>
+    <t>Physiological Tools for Monitoring Urban Impacts at The Roost Level in Insectivorous Bats</t>
+  </si>
+  <si>
+    <t>Bats Are in The Building: Understanding Anthropogenic Roost Selection Through Habitat Models</t>
+  </si>
+  <si>
+    <t>Stressed Out Bats: Developing Tools to Monitor Physiological Stress in Three Insectivorous Species</t>
+  </si>
+  <si>
+    <t>The System Works: Post-Release Survival of Rehabilitated Insectivorous Bats in Australia</t>
+  </si>
+  <si>
+    <t>Home Is Where the Bats Are: Bats in Man-Made Structures in South East Queensland</t>
+  </si>
+  <si>
+    <t>From Rugs to Rocky Overhangs: Diverse Microclimates of Natural and Anthropogenic Bat Roosts in South East Queensland</t>
+  </si>
+  <si>
+    <t>Roosting Ecology of Australian Insectivorous Bats, A Public Dataset</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="167" formatCode="mmm\-yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -553,16 +648,19 @@
       <b/>
       <sz val="14"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -590,7 +688,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -600,11 +698,14 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -906,250 +1007,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:A17"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="100" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="18.75">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:C13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16" customWidth="1"/>
-    <col min="2" max="2" width="26" customWidth="1"/>
-    <col min="3" max="3" width="70" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="30">
-      <c r="A4" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30">
-      <c r="A12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
-      <c r="A13" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -1164,14 +1024,14 @@
     <col min="12" max="12" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="6" t="s">
         <v>22</v>
       </c>
       <c r="D1" s="2" t="s">
@@ -1202,14 +1062,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30">
+    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="4">
-        <v>46023</v>
-      </c>
-      <c r="C2" s="6"/>
+      <c r="B2" s="5">
+        <v>2026</v>
+      </c>
+      <c r="C2" s="5"/>
       <c r="D2" s="3" t="s">
         <v>49</v>
       </c>
@@ -1224,14 +1084,14 @@
       <c r="K2" s="3"/>
       <c r="L2" s="3"/>
     </row>
-    <row r="3" spans="1:12" ht="30">
+    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="4">
-        <v>46023</v>
-      </c>
-      <c r="C3" s="6"/>
+      <c r="B3" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="C3" s="5"/>
       <c r="D3" s="3" t="s">
         <v>51</v>
       </c>
@@ -1246,14 +1106,14 @@
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
     </row>
-    <row r="4" spans="1:12" ht="30">
+    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="4">
-        <v>45658</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B4" s="5">
+        <v>2023</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D4" s="3" t="s">
@@ -1272,15 +1132,15 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
     </row>
-    <row r="5" spans="1:12" ht="30">
+    <row r="5" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="4">
-        <v>43831</v>
-      </c>
-      <c r="C5" s="4">
-        <v>45383</v>
+      <c r="B5" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>162</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>57</v>
@@ -1298,14 +1158,14 @@
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="45">
+    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="4">
-        <v>43466</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B6" s="5">
+        <v>2019</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>53</v>
       </c>
       <c r="D6" s="3" t="s">
@@ -1324,15 +1184,15 @@
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B7" s="4">
-        <v>45292</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>53</v>
+      <c r="B7" s="5">
+        <v>2023</v>
+      </c>
+      <c r="C7" s="5">
+        <v>2026</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>64</v>
@@ -1352,14 +1212,14 @@
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="30">
+    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B8" s="4">
-        <v>45658</v>
-      </c>
-      <c r="C8" s="6"/>
+      <c r="B8" s="5">
+        <v>2025</v>
+      </c>
+      <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
         <v>68</v>
       </c>
@@ -1378,14 +1238,14 @@
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
     </row>
-    <row r="9" spans="1:12" ht="30">
+    <row r="9" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="4">
-        <v>45292</v>
-      </c>
-      <c r="C9" s="6"/>
+      <c r="B9" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
         <v>72</v>
       </c>
@@ -1404,14 +1264,14 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B10" s="4">
-        <v>44927</v>
-      </c>
-      <c r="C10" s="6"/>
+      <c r="B10" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C10" s="5"/>
       <c r="D10" s="3" t="s">
         <v>75</v>
       </c>
@@ -1430,14 +1290,14 @@
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="4">
-        <v>44197</v>
-      </c>
-      <c r="C11" s="6"/>
+      <c r="B11" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="C11" s="5"/>
       <c r="D11" s="3" t="s">
         <v>78</v>
       </c>
@@ -1456,14 +1316,14 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B12" s="4">
-        <v>43831</v>
-      </c>
-      <c r="C12" s="6"/>
+      <c r="B12" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C12" s="5"/>
       <c r="D12" s="3" t="s">
         <v>81</v>
       </c>
@@ -1482,14 +1342,14 @@
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B13" s="4">
-        <v>43831</v>
-      </c>
-      <c r="C13" s="6"/>
+      <c r="B13" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C13" s="5"/>
       <c r="D13" s="3" t="s">
         <v>84</v>
       </c>
@@ -1508,14 +1368,14 @@
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B14" s="4">
-        <v>44927</v>
-      </c>
-      <c r="C14" s="6"/>
+      <c r="B14" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C14" s="5"/>
       <c r="D14" s="3" t="s">
         <v>86</v>
       </c>
@@ -1534,14 +1394,14 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" ht="30">
+    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B15" s="4">
-        <v>46113</v>
-      </c>
-      <c r="C15" s="6"/>
+      <c r="B15" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C15" s="5"/>
       <c r="D15" s="3" t="s">
         <v>90</v>
       </c>
@@ -1556,16 +1416,16 @@
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
-    <row r="16" spans="1:12" ht="30">
+    <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B16" s="4">
-        <v>45931</v>
-      </c>
-      <c r="C16" s="6"/>
+      <c r="B16" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C16" s="5"/>
       <c r="D16" s="3" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1578,14 +1438,14 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="4">
-        <v>45839</v>
-      </c>
-      <c r="C17" s="6"/>
+      <c r="B17" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C17" s="5"/>
       <c r="D17" s="3" t="s">
         <v>93</v>
       </c>
@@ -1600,14 +1460,14 @@
       <c r="K17" s="3"/>
       <c r="L17" s="3"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B18" s="4">
-        <v>45536</v>
-      </c>
-      <c r="C18" s="6"/>
+      <c r="B18" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C18" s="5"/>
       <c r="D18" s="3" t="s">
         <v>94</v>
       </c>
@@ -1622,383 +1482,383 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="45">
+    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B19" s="4">
-        <v>46235</v>
-      </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="3" t="s">
+      <c r="B19" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="C19" s="5"/>
+      <c r="D19" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>95</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>96</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
     </row>
-    <row r="20" spans="1:12" ht="45">
+    <row r="20" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B20" s="4">
-        <v>45962</v>
-      </c>
-      <c r="C20" s="6"/>
-      <c r="D20" s="3" t="s">
-        <v>98</v>
+      <c r="B20" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C20" s="5"/>
+      <c r="D20" s="8" t="s">
+        <v>194</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="1:12" ht="45">
+    <row r="21" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B21" s="4">
-        <v>45992</v>
-      </c>
-      <c r="C21" s="6"/>
-      <c r="D21" s="3" t="s">
-        <v>100</v>
+      <c r="B21" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="C21" s="5"/>
+      <c r="D21" s="8" t="s">
+        <v>195</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
       <c r="K21" s="3"/>
       <c r="L21" s="3"/>
     </row>
-    <row r="22" spans="1:12" ht="45">
+    <row r="22" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="4">
-        <v>45870</v>
-      </c>
-      <c r="C22" s="6"/>
-      <c r="D22" s="3" t="s">
-        <v>167</v>
+      <c r="B22" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C22" s="5"/>
+      <c r="D22" s="8" t="s">
+        <v>160</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="30">
+    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B23" s="4">
-        <v>45871</v>
-      </c>
-      <c r="C23" s="6"/>
-      <c r="D23" s="3" t="s">
-        <v>103</v>
+      <c r="B23" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C23" s="5"/>
+      <c r="D23" s="8" t="s">
+        <v>196</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
       <c r="K23" s="3"/>
       <c r="L23" s="3"/>
     </row>
-    <row r="24" spans="1:12" ht="30">
+    <row r="24" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="4">
-        <v>45839</v>
-      </c>
-      <c r="C24" s="6"/>
-      <c r="D24" s="3" t="s">
-        <v>104</v>
+      <c r="B24" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="5"/>
+      <c r="D24" s="8" t="s">
+        <v>197</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="45">
+    <row r="25" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B25" s="4">
-        <v>45383</v>
-      </c>
-      <c r="C25" s="6"/>
-      <c r="D25" s="3" t="s">
-        <v>106</v>
+      <c r="B25" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C25" s="5"/>
+      <c r="D25" s="8" t="s">
+        <v>198</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="30">
+    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B26" s="4">
-        <v>45384</v>
-      </c>
-      <c r="C26" s="6"/>
-      <c r="D26" s="3" t="s">
-        <v>108</v>
+      <c r="B26" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="5"/>
+      <c r="D26" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
-    <row r="27" spans="1:12" ht="30">
+    <row r="27" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="4">
-        <v>45566</v>
-      </c>
-      <c r="C27" s="6"/>
-      <c r="D27" s="3" t="s">
-        <v>108</v>
+      <c r="B27" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C27" s="5"/>
+      <c r="D27" s="8" t="s">
+        <v>199</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>112</v>
+        <v>105</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="45">
+    <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B28" s="4">
-        <v>45231</v>
-      </c>
-      <c r="C28" s="6"/>
+      <c r="B28" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C28" s="5"/>
       <c r="D28" s="3" t="s">
-        <v>113</v>
+        <v>106</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>114</v>
+        <v>107</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="30">
+    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="4">
-        <v>43862</v>
-      </c>
-      <c r="C29" s="6"/>
+      <c r="B29" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="45">
+    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B30" s="4">
-        <v>43800</v>
-      </c>
-      <c r="C30" s="6"/>
+      <c r="B30" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
       <c r="K30" s="3"/>
       <c r="L30" s="3"/>
     </row>
-    <row r="31" spans="1:12" ht="45">
+    <row r="31" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B31" s="4">
-        <v>43374</v>
-      </c>
-      <c r="C31" s="6"/>
+      <c r="B31" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="30">
+    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="4">
-        <v>42095</v>
-      </c>
-      <c r="C32" s="6"/>
+      <c r="B32" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="45">
+    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B33" s="4">
-        <v>42461</v>
-      </c>
-      <c r="C33" s="6"/>
+      <c r="B33" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="30">
+    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B34" s="4">
-        <v>46050</v>
-      </c>
-      <c r="C34" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C34" s="5"/>
       <c r="D34" s="3" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -2008,19 +1868,19 @@
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
-    <row r="35" spans="1:12" ht="30">
+    <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="4">
-        <v>46047</v>
-      </c>
-      <c r="C35" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="5"/>
       <c r="D35" s="3" t="s">
-        <v>129</v>
+        <v>122</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>130</v>
+        <v>123</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -2030,19 +1890,19 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="45">
+    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B36" s="4">
-        <v>45532</v>
-      </c>
-      <c r="C36" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C36" s="5"/>
       <c r="D36" s="3" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -2050,23 +1910,23 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="L36" s="3"/>
     </row>
-    <row r="37" spans="1:12" ht="45">
+    <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B37" s="4">
-        <v>45498</v>
-      </c>
-      <c r="C37" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="C37" s="5"/>
       <c r="D37" s="3" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -2074,23 +1934,23 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="L37" s="3"/>
     </row>
-    <row r="38" spans="1:12" ht="45">
+    <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B38" s="4">
-        <v>45345</v>
-      </c>
-      <c r="C38" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="C38" s="5"/>
       <c r="D38" s="3" t="s">
-        <v>137</v>
+        <v>130</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -2098,23 +1958,23 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B39" s="4">
-        <v>45331</v>
-      </c>
-      <c r="C39" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="5"/>
       <c r="D39" s="3" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>141</v>
+        <v>134</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -2124,19 +1984,19 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12" ht="30">
+    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="B40" s="4">
-        <v>45132</v>
-      </c>
-      <c r="C40" s="6"/>
+        <v>119</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="5"/>
       <c r="D40" s="3" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -2144,23 +2004,23 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B41" s="4">
-        <v>46082</v>
-      </c>
-      <c r="C41" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C41" s="5"/>
       <c r="D41" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -2170,19 +2030,19 @@
       <c r="K41" s="3"/>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12" ht="30">
+    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B42" s="4">
-        <v>46083</v>
-      </c>
-      <c r="C42" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="C42" s="5"/>
       <c r="D42" s="3" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2192,19 +2052,19 @@
       <c r="K42" s="3"/>
       <c r="L42" s="3"/>
     </row>
-    <row r="43" spans="1:12" ht="30">
+    <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B43" s="4">
-        <v>45962</v>
-      </c>
-      <c r="C43" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C43" s="5"/>
       <c r="D43" s="3" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2214,19 +2074,19 @@
       <c r="K43" s="3"/>
       <c r="L43" s="3"/>
     </row>
-    <row r="44" spans="1:12" ht="30">
+    <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B44" s="4">
-        <v>45931</v>
-      </c>
-      <c r="C44" s="6"/>
-      <c r="D44" s="3" t="s">
-        <v>152</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2236,19 +2096,19 @@
       <c r="K44" s="3"/>
       <c r="L44" s="3"/>
     </row>
-    <row r="45" spans="1:12" ht="30">
+    <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B45" s="4">
-        <v>45932</v>
-      </c>
-      <c r="C45" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C45" s="5"/>
       <c r="D45" s="3" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2258,16 +2118,16 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="4">
-        <v>45597</v>
-      </c>
-      <c r="C46" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C46" s="5"/>
       <c r="D46" s="3" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>55</v>
@@ -2280,19 +2140,19 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12" ht="30">
+    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B47" s="4">
-        <v>45566</v>
-      </c>
-      <c r="C47" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="5"/>
       <c r="D47" s="3" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2302,19 +2162,19 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12">
+    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B48" s="4">
-        <v>45567</v>
-      </c>
-      <c r="C48" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="5"/>
       <c r="D48" s="3" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2324,19 +2184,19 @@
       <c r="K48" s="3"/>
       <c r="L48" s="3"/>
     </row>
-    <row r="49" spans="1:12">
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B49" s="4">
-        <v>45536</v>
-      </c>
-      <c r="C49" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C49" s="5"/>
       <c r="D49" s="3" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2346,19 +2206,19 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" ht="30">
+    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B50" s="4">
-        <v>45413</v>
-      </c>
-      <c r="C50" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="C50" s="5"/>
       <c r="D50" s="3" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2368,19 +2228,19 @@
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
-    <row r="51" spans="1:12" ht="30">
+    <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" s="4">
-        <v>45383</v>
-      </c>
-      <c r="C51" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C51" s="5"/>
       <c r="D51" s="3" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2390,19 +2250,19 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="1:12">
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B52" s="4">
-        <v>45200</v>
-      </c>
-      <c r="C52" s="6"/>
+        <v>138</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="C52" s="5"/>
       <c r="D52" s="3" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2416,4 +2276,245 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:C13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:A17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="100" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA857865-E8FB-4063-9B4E-3C453DBCF897}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5144B9-183C-498E-BBB7-39C9E71D2D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C5144B9-183C-498E-BBB7-39C9E71D2D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01952EF-9C04-46DD-B2E6-D568011EF990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -227,9 +227,6 @@
     <t>Holsworth Wildlife Research Endowment</t>
   </si>
   <si>
-    <t>$20,720</t>
-  </si>
-  <si>
     <t>Lead Author</t>
   </si>
   <si>
@@ -239,9 +236,6 @@
     <t>GBatNet Global Union of Bat Diversity Networks</t>
   </si>
   <si>
-    <t>$21,851</t>
-  </si>
-  <si>
     <t>Co-investigator</t>
   </si>
   <si>
@@ -251,51 +245,33 @@
     <t>WIRES National Research Grant</t>
   </si>
   <si>
-    <t>$49,586</t>
-  </si>
-  <si>
     <t>Radio Transmitters for Insectivorous Bats</t>
   </si>
   <si>
     <t>Holohil Transmitter Grant Program</t>
   </si>
   <si>
-    <t>$2,720</t>
-  </si>
-  <si>
     <t>Wildlife Corridors in the Scenic Rim</t>
   </si>
   <si>
     <t>Landcare Led Bushfire Recovery Grants</t>
   </si>
   <si>
-    <t>$49,000</t>
-  </si>
-  <si>
     <t>Educational Workshops and Events for Bat Carers</t>
   </si>
   <si>
     <t>Logan EnviroGrants</t>
   </si>
   <si>
-    <t>$1,950</t>
-  </si>
-  <si>
     <t>ICUs for Bat Carers Capacity Building</t>
   </si>
   <si>
-    <t>$9,900</t>
-  </si>
-  <si>
     <t>Bat Roost Identification</t>
   </si>
   <si>
     <t>Wildlife Acoustics Scientific Product Grant</t>
   </si>
   <si>
-    <t>$1,197</t>
-  </si>
-  <si>
     <t>seminars</t>
   </si>
   <si>
@@ -627,16 +603,41 @@
   </si>
   <si>
     <t>Roosting Ecology of Australian Insectivorous Bats, A Public Dataset</t>
+  </si>
+  <si>
+    <t>20,720</t>
+  </si>
+  <si>
+    <t>21,851</t>
+  </si>
+  <si>
+    <t>49,586</t>
+  </si>
+  <si>
+    <t>49,000</t>
+  </si>
+  <si>
+    <t>9,900</t>
+  </si>
+  <si>
+    <t>1,950</t>
+  </si>
+  <si>
+    <t>2,720</t>
+  </si>
+  <si>
+    <t>1,197</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -662,6 +663,13 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -685,10 +693,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -706,8 +715,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1089,7 +1102,7 @@
         <v>48</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="3" t="s">
@@ -1137,10 +1150,10 @@
         <v>48</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>57</v>
@@ -1203,11 +1216,11 @@
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>66</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>67</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
@@ -1221,19 +1234,19 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>68</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>69</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
-      <c r="I8" s="3" t="s">
-        <v>70</v>
+      <c r="I8" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1243,23 +1256,23 @@
         <v>63</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
-        <v>74</v>
+      <c r="I9" s="9" t="s">
+        <v>194</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
@@ -1269,23 +1282,23 @@
         <v>63</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="3" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
-      <c r="I10" s="3" t="s">
-        <v>77</v>
+      <c r="I10" s="9" t="s">
+        <v>198</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1295,23 +1308,23 @@
         <v>63</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="3" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-      <c r="I11" s="3" t="s">
-        <v>80</v>
+      <c r="I11" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -1321,23 +1334,23 @@
         <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="3" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-      <c r="I12" s="3" t="s">
-        <v>83</v>
+      <c r="I12" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -1347,23 +1360,23 @@
         <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="3" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
-        <v>85</v>
+      <c r="I13" s="9" t="s">
+        <v>196</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -1373,42 +1386,42 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="3" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-      <c r="I14" s="3" t="s">
-        <v>88</v>
+      <c r="I14" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
     <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="3" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
@@ -1418,19 +1431,19 @@
     </row>
     <row r="16" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -1440,14 +1453,14 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="3" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
@@ -1462,14 +1475,14 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="3" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1487,19 +1500,19 @@
         <v>35</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="8" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
@@ -1511,19 +1524,19 @@
         <v>35</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="8" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I20" s="3"/>
       <c r="J20" s="3"/>
@@ -1535,19 +1548,19 @@
         <v>35</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="8" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I21" s="3"/>
       <c r="J21" s="3"/>
@@ -1559,19 +1572,19 @@
         <v>35</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I22" s="3"/>
       <c r="J22" s="3"/>
@@ -1583,19 +1596,19 @@
         <v>35</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="8" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I23" s="3"/>
       <c r="J23" s="3"/>
@@ -1607,19 +1620,19 @@
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I24" s="3"/>
       <c r="J24" s="3"/>
@@ -1631,19 +1644,19 @@
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
       <c r="H25" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I25" s="3"/>
       <c r="J25" s="3"/>
@@ -1655,23 +1668,23 @@
         <v>35</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I26" s="3"/>
       <c r="J26" s="3" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -1681,19 +1694,19 @@
         <v>35</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
       <c r="H27" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I27" s="3"/>
       <c r="J27" s="3"/>
@@ -1705,19 +1718,19 @@
         <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="C28" s="5"/>
       <c r="D28" s="3" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
@@ -1729,19 +1742,19 @@
         <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
       <c r="H29" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I29" s="3"/>
       <c r="J29" s="3"/>
@@ -1753,19 +1766,19 @@
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
       <c r="H30" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I30" s="3"/>
       <c r="J30" s="3"/>
@@ -1777,19 +1790,19 @@
         <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
       <c r="H31" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I31" s="3"/>
       <c r="J31" s="3"/>
@@ -1801,19 +1814,19 @@
         <v>35</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
@@ -1825,40 +1838,40 @@
         <v>35</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="I33" s="3"/>
       <c r="J33" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
     <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
@@ -1870,17 +1883,17 @@
     </row>
     <row r="35" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -1892,17 +1905,17 @@
     </row>
     <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
@@ -1910,23 +1923,23 @@
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="L36" s="3"/>
     </row>
     <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -1934,23 +1947,23 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="L37" s="3"/>
     </row>
     <row r="38" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1958,23 +1971,23 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="L38" s="3"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="3" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
@@ -1986,17 +1999,17 @@
     </row>
     <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="3" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
@@ -2004,23 +2017,23 @@
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="L40" s="3"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
@@ -2032,17 +2045,17 @@
     </row>
     <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="3" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2054,17 +2067,17 @@
     </row>
     <row r="43" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="3" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2076,17 +2089,17 @@
     </row>
     <row r="44" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="3" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2098,17 +2111,17 @@
     </row>
     <row r="45" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="3" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2120,14 +2133,14 @@
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="E46" s="3" t="s">
         <v>55</v>
@@ -2142,17 +2155,17 @@
     </row>
     <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="3" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2164,17 +2177,17 @@
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="3" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2186,17 +2199,17 @@
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="3" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2208,17 +2221,17 @@
     </row>
     <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="3" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2230,17 +2243,17 @@
     </row>
     <row r="51" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2252,17 +2265,17 @@
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>

--- a/cv/cv_data.xlsx
+++ b/cv/cv_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\usc.internal\usc\studenthome\r_r113\Documents\GitHubRepo\GitHub\RobinERowland.github.io\cv\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01952EF-9C04-46DD-B2E6-D568011EF990}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{305F4627-6A3B-4B88-B8F7-CCCEC4D2BD07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="202">
   <si>
     <t>cv_data.xlsx - how this works</t>
   </si>
@@ -627,6 +627,12 @@
   </si>
   <si>
     <t>1,197</t>
+  </si>
+  <si>
+    <t>School of Science, Technology and Engineering Research Conference</t>
+  </si>
+  <si>
+    <t>Best Student Poster</t>
   </si>
 </sst>
 </file>
@@ -637,7 +643,7 @@
     <numFmt numFmtId="44" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -670,6 +676,18 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -697,7 +715,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -718,6 +736,11 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="17" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1021,7 +1044,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L52"/>
+  <dimension ref="A1:L53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -1075,38 +1098,42 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B2" s="5">
-        <v>2026</v>
-      </c>
-      <c r="C2" s="5"/>
-      <c r="D2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
+        <v>35</v>
+      </c>
+      <c r="B2" s="13">
+        <v>45474</v>
+      </c>
+      <c r="C2" s="11"/>
+      <c r="D2" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="E2" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="I2" s="10"/>
+      <c r="J2" s="14" t="s">
+        <v>201</v>
+      </c>
+      <c r="K2" s="10"/>
+      <c r="L2" s="10"/>
     </row>
     <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>153</v>
+      <c r="B3" s="5">
+        <v>2026</v>
       </c>
       <c r="C3" s="5"/>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3"/>
       <c r="F3" s="3"/>
@@ -1114,7 +1141,7 @@
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
@@ -1123,24 +1150,20 @@
       <c r="A4" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B4" s="5">
-        <v>2023</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>53</v>
-      </c>
+      <c r="B4" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="5"/>
       <c r="D4" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>55</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="E4" s="3"/>
       <c r="F4" s="3"/>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -1149,104 +1172,104 @@
       <c r="A5" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>157</v>
+      <c r="B5" s="5">
+        <v>2023</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>154</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F5" s="3"/>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
       <c r="J5" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="K5" s="3"/>
       <c r="L5" s="3"/>
     </row>
-    <row r="6" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="5">
-        <v>2019</v>
+      <c r="B6" s="5" t="s">
+        <v>157</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>53</v>
+        <v>154</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F6" s="3"/>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
       <c r="I6" s="3"/>
       <c r="J6" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K6" s="3"/>
       <c r="L6" s="3"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B7" s="5">
-        <v>2023</v>
-      </c>
-      <c r="C7" s="5">
-        <v>2026</v>
+        <v>2019</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>53</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="F7" s="3"/>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
-      <c r="I7" s="9" t="s">
-        <v>192</v>
-      </c>
+      <c r="I7" s="3"/>
       <c r="J7" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="K7" s="3"/>
       <c r="L7" s="3"/>
     </row>
-    <row r="8" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B8" s="5">
-        <v>2025</v>
-      </c>
-      <c r="C8" s="5"/>
+        <v>2023</v>
+      </c>
+      <c r="C8" s="5">
+        <v>2026</v>
+      </c>
       <c r="D8" s="3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F8" s="3"/>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
       <c r="I8" s="9" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K8" s="3"/>
       <c r="L8" s="3"/>
@@ -1255,21 +1278,21 @@
       <c r="A9" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>154</v>
+      <c r="B9" s="5">
+        <v>2025</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="3" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
       <c r="I9" s="9" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J9" s="3" t="s">
         <v>69</v>
@@ -1277,28 +1300,28 @@
       <c r="K9" s="3"/>
       <c r="L9" s="3"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>63</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
       <c r="I10" s="9" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -1308,20 +1331,20 @@
         <v>63</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="3" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
       <c r="I11" s="9" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>66</v>
@@ -1334,20 +1357,20 @@
         <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
       <c r="I12" s="9" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>66</v>
@@ -1364,7 +1387,7 @@
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="3" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>77</v>
@@ -1373,7 +1396,7 @@
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="9" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>66</v>
@@ -1386,20 +1409,20 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
       <c r="I14" s="9" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>66</v>
@@ -1407,25 +1430,29 @@
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
     </row>
-    <row r="15" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>159</v>
+        <v>63</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>155</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" s="3"/>
+        <v>79</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>80</v>
+      </c>
       <c r="F15" s="3"/>
-      <c r="G15" s="3" t="s">
-        <v>83</v>
-      </c>
+      <c r="G15" s="3"/>
       <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3"/>
+      <c r="I15" s="9" t="s">
+        <v>199</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>66</v>
+      </c>
       <c r="K15" s="3"/>
       <c r="L15" s="3"/>
     </row>
@@ -1434,16 +1461,16 @@
         <v>81</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="3" t="s">
-        <v>151</v>
+        <v>82</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
@@ -1451,21 +1478,21 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>81</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="3" t="s">
-        <v>85</v>
+        <v>151</v>
       </c>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3" t="s">
-        <v>55</v>
+        <v>84</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
@@ -1478,11 +1505,11 @@
         <v>81</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C18" s="5"/>
       <c r="D18" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="3"/>
@@ -1495,25 +1522,23 @@
       <c r="K18" s="3"/>
       <c r="L18" s="3"/>
     </row>
-    <row r="19" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C19" s="5"/>
-      <c r="D19" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>87</v>
-      </c>
+      <c r="D19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="3"/>
       <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>88</v>
-      </c>
+      <c r="G19" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3"/>
       <c r="J19" s="3"/>
       <c r="K19" s="3"/>
@@ -1524,14 +1549,14 @@
         <v>35</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="8" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
@@ -1548,14 +1573,14 @@
         <v>35</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="8" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
@@ -1572,14 +1597,14 @@
         <v>35</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="8" t="s">
-        <v>152</v>
+        <v>187</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
@@ -1591,7 +1616,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>35</v>
       </c>
@@ -1600,7 +1625,7 @@
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="8" t="s">
-        <v>188</v>
+        <v>152</v>
       </c>
       <c r="E23" s="3" t="s">
         <v>91</v>
@@ -1620,14 +1645,14 @@
         <v>35</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C24" s="5"/>
       <c r="D24" s="8" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
@@ -1639,19 +1664,19 @@
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
-    <row r="25" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C25" s="5"/>
       <c r="D25" s="8" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F25" s="3"/>
       <c r="G25" s="3"/>
@@ -1663,7 +1688,7 @@
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
-    <row r="26" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
         <v>35</v>
       </c>
@@ -1672,20 +1697,18 @@
       </c>
       <c r="C26" s="5"/>
       <c r="D26" s="8" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F26" s="3"/>
       <c r="G26" s="3"/>
       <c r="H26" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I26" s="3"/>
-      <c r="J26" s="3" t="s">
-        <v>96</v>
-      </c>
+      <c r="J26" s="3"/>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
@@ -1694,14 +1717,14 @@
         <v>35</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="C27" s="5"/>
       <c r="D27" s="8" t="s">
         <v>191</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F27" s="3"/>
       <c r="G27" s="3"/>
@@ -1709,47 +1732,49 @@
         <v>95</v>
       </c>
       <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
+      <c r="J27" s="3" t="s">
+        <v>96</v>
+      </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
-    <row r="28" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C28" s="5"/>
-      <c r="D28" s="3" t="s">
-        <v>98</v>
+      <c r="D28" s="8" t="s">
+        <v>191</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F28" s="3"/>
       <c r="G28" s="3"/>
       <c r="H28" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I28" s="3"/>
       <c r="J28" s="3"/>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
-    <row r="29" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F29" s="3"/>
       <c r="G29" s="3"/>
@@ -1761,19 +1786,19 @@
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
     </row>
-    <row r="30" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C30" s="5"/>
       <c r="D30" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F30" s="3"/>
       <c r="G30" s="3"/>
@@ -1790,14 +1815,14 @@
         <v>35</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C31" s="5"/>
       <c r="D31" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F31" s="3"/>
       <c r="G31" s="3"/>
@@ -1809,75 +1834,77 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
     </row>
-    <row r="32" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C32" s="5"/>
       <c r="D32" s="3" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="F32" s="3"/>
       <c r="G32" s="3"/>
       <c r="H32" s="3" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="I32" s="3"/>
       <c r="J32" s="3"/>
       <c r="K32" s="3"/>
       <c r="L32" s="3"/>
     </row>
-    <row r="33" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C33" s="5"/>
       <c r="D33" s="3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F33" s="3"/>
       <c r="G33" s="3"/>
       <c r="H33" s="3" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I33" s="3"/>
-      <c r="J33" s="3" t="s">
-        <v>110</v>
-      </c>
+      <c r="J33" s="3"/>
       <c r="K33" s="3"/>
       <c r="L33" s="3"/>
     </row>
-    <row r="34" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>111</v>
+        <v>35</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C34" s="5"/>
       <c r="D34" s="3" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="F34" s="3"/>
       <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
+      <c r="H34" s="3" t="s">
+        <v>88</v>
+      </c>
       <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
+      <c r="J34" s="3" t="s">
+        <v>110</v>
+      </c>
       <c r="K34" s="3"/>
       <c r="L34" s="3"/>
     </row>
@@ -1886,14 +1913,14 @@
         <v>111</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C35" s="5"/>
       <c r="D35" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F35" s="3"/>
       <c r="G35" s="3"/>
@@ -1903,28 +1930,26 @@
       <c r="K35" s="3"/>
       <c r="L35" s="3"/>
     </row>
-    <row r="36" spans="1:12" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C36" s="5"/>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F36" s="3"/>
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
       <c r="J36" s="3"/>
-      <c r="K36" s="3" t="s">
-        <v>118</v>
-      </c>
+      <c r="K36" s="3"/>
       <c r="L36" s="3"/>
     </row>
     <row r="37" spans="1:12" ht="45" x14ac:dyDescent="0.25">
@@ -1932,14 +1957,14 @@
         <v>111</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C37" s="5"/>
       <c r="D37" s="3" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F37" s="3"/>
       <c r="G37" s="3"/>
@@ -1947,7 +1972,7 @@
       <c r="I37" s="3"/>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="L37" s="3"/>
     </row>
@@ -1956,14 +1981,14 @@
         <v>111</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="3" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F38" s="3"/>
       <c r="G38" s="3"/>
@@ -1971,79 +1996,81 @@
       <c r="I38" s="3"/>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="L38" s="3"/>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C39" s="5"/>
       <c r="D39" s="3" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="F39" s="3"/>
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
       <c r="J39" s="3"/>
-      <c r="K39" s="3"/>
+      <c r="K39" s="3" t="s">
+        <v>124</v>
+      </c>
       <c r="L39" s="3"/>
     </row>
-    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
         <v>111</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C40" s="5"/>
       <c r="D40" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3"/>
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
       <c r="J40" s="3"/>
-      <c r="K40" s="3" t="s">
-        <v>129</v>
-      </c>
+      <c r="K40" s="3"/>
       <c r="L40" s="3"/>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C41" s="5"/>
       <c r="D41" s="3" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3"/>
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
       <c r="J41" s="3"/>
-      <c r="K41" s="3"/>
+      <c r="K41" s="3" t="s">
+        <v>129</v>
+      </c>
       <c r="L41" s="3"/>
     </row>
-    <row r="42" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
         <v>130</v>
       </c>
@@ -2052,10 +2079,10 @@
       </c>
       <c r="C42" s="5"/>
       <c r="D42" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F42" s="3"/>
       <c r="G42" s="3"/>
@@ -2070,14 +2097,14 @@
         <v>130</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>164</v>
+        <v>181</v>
       </c>
       <c r="C43" s="5"/>
       <c r="D43" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="F43" s="3"/>
       <c r="G43" s="3"/>
@@ -2092,14 +2119,14 @@
         <v>130</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C44" s="5"/>
       <c r="D44" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F44" s="3"/>
       <c r="G44" s="3"/>
@@ -2118,10 +2145,10 @@
       </c>
       <c r="C45" s="5"/>
       <c r="D45" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3"/>
@@ -2131,19 +2158,19 @@
       <c r="K45" s="3"/>
       <c r="L45" s="3"/>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>182</v>
+        <v>160</v>
       </c>
       <c r="C46" s="5"/>
       <c r="D46" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>55</v>
+        <v>140</v>
       </c>
       <c r="F46" s="3"/>
       <c r="G46" s="3"/>
@@ -2153,19 +2180,19 @@
       <c r="K46" s="3"/>
       <c r="L46" s="3"/>
     </row>
-    <row r="47" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="C47" s="5"/>
       <c r="D47" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>136</v>
+        <v>55</v>
       </c>
       <c r="F47" s="3"/>
       <c r="G47" s="3"/>
@@ -2175,7 +2202,7 @@
       <c r="K47" s="3"/>
       <c r="L47" s="3"/>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
         <v>130</v>
       </c>
@@ -2184,10 +2211,10 @@
       </c>
       <c r="C48" s="5"/>
       <c r="D48" s="3" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F48" s="3"/>
       <c r="G48" s="3"/>
@@ -2202,14 +2229,14 @@
         <v>130</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C49" s="5"/>
       <c r="D49" s="3" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F49" s="3"/>
       <c r="G49" s="3"/>
@@ -2219,19 +2246,19 @@
       <c r="K49" s="3"/>
       <c r="L49" s="3"/>
     </row>
-    <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>183</v>
+        <v>162</v>
       </c>
       <c r="C50" s="5"/>
       <c r="D50" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F50" s="3"/>
       <c r="G50" s="3"/>
@@ -2246,14 +2273,14 @@
         <v>130</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>158</v>
+        <v>183</v>
       </c>
       <c r="C51" s="5"/>
       <c r="D51" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F51" s="3"/>
       <c r="G51" s="3"/>
@@ -2263,19 +2290,19 @@
       <c r="K51" s="3"/>
       <c r="L51" s="3"/>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
         <v>130</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>184</v>
+        <v>158</v>
       </c>
       <c r="C52" s="5"/>
       <c r="D52" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F52" s="3"/>
       <c r="G52" s="3"/>
@@ -2284,6 +2311,28 @@
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C53" s="5"/>
+      <c r="D53" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="F53" s="3"/>
+      <c r="G53" s="3"/>
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="K53" s="3"/>
+      <c r="L53" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
